--- a/bond_analysis_results_2026-02-04.xlsx
+++ b/bond_analysis_results_2026-02-04.xlsx
@@ -1006,7 +1006,7 @@
           <t>备注：
 1. 优先按照投资天数需求选择，再根据税后收益率排名获得购买结果。
 2. 所列债券日成交额均大于10亿，流动性有保证。
-3. 推荐购买6个月内的债券，是现金等价物。</t>
+3. 推荐购买6个月内的债券，属于无风险的现金等价物。</t>
         </is>
       </c>
     </row>
